--- a/output/laminas_comunales/comunal_o_ocup_a_2021_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2021_tarapaca.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,67 +384,517 @@
         </is>
       </c>
       <c r="C2">
-        <v>37.8162557206666</v>
+        <v>53.3756697013975</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
+          <t>Pica</t>
         </is>
       </c>
       <c r="C3">
-        <v>35.934083973168</v>
+        <v>47.835583796664</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
+          <t>Iquique</t>
         </is>
       </c>
       <c r="C4">
-        <v>34.0471871822354</v>
+        <v>47.6240330754868</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pica</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="C5">
-        <v>30.0909834389695</v>
+        <v>47.4391342483939</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>46.4754024235847</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>44.0839820920539</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>42.6370528199272</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>41.7130919220056</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>40.8368859114901</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>40.7313440371605</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>37.8162557206666</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>1404</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Huara</t>
         </is>
       </c>
-      <c r="C6">
+      <c r="C13">
+        <v>36.6759950248756</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>35.934083973168</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>35.6395747599451</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>34.9753694581281</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>34.0471871822354</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>33.9339339339339</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>32.9928467388274</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>31.5279770444763</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>31.4903469721035</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>30.7569558101473</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>30.7117868675996</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>30.0909834389695</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>28.4413580246914</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>27.5360013332424</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>26.2590172859671</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>26.0279925672841</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C29">
         <v>24.6697277267601</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>22.9843073593074</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>20.5510616784631</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>11.9739909213593</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>11.1085990450908</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>10.252935862692</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>6.60215903106898</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>5.91976516634051</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_o_ocup_a_2021_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2021_tarapaca.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,517 +384,67 @@
         </is>
       </c>
       <c r="C2">
-        <v>53.3756697013975</v>
+        <v>37.8162557206666</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pica</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="C3">
-        <v>47.835583796664</v>
+        <v>35.934083973168</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Iquique</t>
+          <t>Pozo Almonte</t>
         </is>
       </c>
       <c r="C4">
-        <v>47.6240330754868</v>
+        <v>34.0471871822354</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
+          <t>Pica</t>
         </is>
       </c>
       <c r="C5">
-        <v>47.4391342483939</v>
+        <v>30.0909834389695</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
+          <t>Huara</t>
         </is>
       </c>
       <c r="C6">
-        <v>46.4754024235847</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1107</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Alto Hospicio</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>44.0839820920539</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Iquique</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>42.6370528199272</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Pozo Almonte</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>41.7130919220056</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Pozo Almonte</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>40.8368859114901</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1107</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Alto Hospicio</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>40.7313440371605</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Iquique</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>37.8162557206666</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>1404</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Huara</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>36.6759950248756</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1107</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Alto Hospicio</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>35.934083973168</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Pica</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>35.6395747599451</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>1404</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Huara</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>34.9753694581281</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Pozo Almonte</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>34.0471871822354</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Pica</t>
-        </is>
-      </c>
-      <c r="C18">
-        <v>33.9339339339339</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Iquique</t>
-        </is>
-      </c>
-      <c r="C19">
-        <v>32.9928467388274</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Pica</t>
-        </is>
-      </c>
-      <c r="C20">
-        <v>31.5279770444763</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Iquique</t>
-        </is>
-      </c>
-      <c r="C21">
-        <v>31.4903469721035</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>1107</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Alto Hospicio</t>
-        </is>
-      </c>
-      <c r="C22">
-        <v>30.7569558101473</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Pozo Almonte</t>
-        </is>
-      </c>
-      <c r="C23">
-        <v>30.7117868675996</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Pica</t>
-        </is>
-      </c>
-      <c r="C24">
-        <v>30.0909834389695</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>1404</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Huara</t>
-        </is>
-      </c>
-      <c r="C25">
-        <v>28.4413580246914</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>1107</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Alto Hospicio</t>
-        </is>
-      </c>
-      <c r="C26">
-        <v>27.5360013332424</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Pica</t>
-        </is>
-      </c>
-      <c r="C27">
-        <v>26.2590172859671</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Pozo Almonte</t>
-        </is>
-      </c>
-      <c r="C28">
-        <v>26.0279925672841</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>1404</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Huara</t>
-        </is>
-      </c>
-      <c r="C29">
         <v>24.6697277267601</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1404</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Huara</t>
-        </is>
-      </c>
-      <c r="C30">
-        <v>22.9843073593074</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>1404</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Huara</t>
-        </is>
-      </c>
-      <c r="C31">
-        <v>20.5510616784631</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>1107</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Alto Hospicio</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>11.9739909213593</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Iquique</t>
-        </is>
-      </c>
-      <c r="C33">
-        <v>11.1085990450908</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Pozo Almonte</t>
-        </is>
-      </c>
-      <c r="C34">
-        <v>10.252935862692</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Pica</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>6.60215903106898</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>1404</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Huara</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>5.91976516634051</v>
       </c>
     </row>
   </sheetData>
